--- a/2026_09_21/LSLS/LSLS_report_2026-09-25.xlsx
+++ b/2026_09_21/LSLS/LSLS_report_2026-09-25.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenalee\work\2026_09\2026_09_21\LSLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81572C3B-98F4-4DCE-8F77-B1EA69CFA6C5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CD9E5D7-4EB8-4823-8B11-D71172501D7D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19560" windowHeight="12405" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19560" windowHeight="12405" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="reduction of salt.sugar" sheetId="1" r:id="rId1"/>
@@ -47,49 +47,49 @@
     <t>App</t>
   </si>
   <si>
-    <t>少鹽少糖食店 Daily Theme Listing Impressions</t>
+    <t>少鹽少糖食店 Daily Theme Listing Impressions (adv search)</t>
   </si>
   <si>
-    <t>11:26:28|| view.SR1.Promotion| CityID:0;PromotionID:13%2C13%2C13%2C13%2C13%2C13%2C13%2C13%2C13%2C12%2C13%2C13%2C13%2C13%2C13%2C13;;Lang:zh_TW;Ver:7.20.4; sn:hk.LMS2.35336.tab.-990.1</t>
+    <t>2. Daily Brand Page (LMS) Pageview/ Impressions</t>
+  </si>
+  <si>
+    <t>3. Daily Theme Listing Impressions (adv search)</t>
+  </si>
+  <si>
+    <t>web</t>
+  </si>
+  <si>
+    <t>Brand Page</t>
+  </si>
+  <si>
+    <t>CityID:0;PromotionId:13,13,13,13,13,13,13,13,13,13,13,13,13,13,13;Sn:https://www.openrice.com/zh/hongkong/l-%E5%B0%91%E9%B9%BD%E5%B0%91%E7%B3%96%E9%A3%9F%E5%BA%97-l35336</t>
+  </si>
+  <si>
+    <t>view.SR1.Promotion</t>
+  </si>
+  <si>
+    <t>CityID:0;PromotionId:13,13,13,13,13,13,13,13,13,13,13,13,13,13,13;Sn:https://www.openrice.com/zh/hongkong/l-%E5%B0%91%E9%B9%BD%E5%B0%91%E7%B3%96%E9%A3%9F%E5%BA%97-l35336?sortBy=ORScoreDesc</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Theme Listing</t>
+  </si>
+  <si>
+    <t>CityID:0;PromotionId:13,13,13,13,13,13,13,13,13,13,13,13,13,13,13;Sn:https://www.openrice.com/zh/hongkong/restaurants/type/%E5%B0%91%E9%B9%BD%E5%B0%91%E7%B3%96%E9%A3%9F%E5%BA%97?sortBy=ORScoreDesc</t>
+  </si>
+  <si>
+    <t>APP</t>
+  </si>
+  <si>
+    <t>11:25:26|| or.search.layer.search| CityID:0;geo:22.2915762%2C114.2081518;LndID:35336;Page:1;sr:lmsSr1;Lang:zh_TW;Ver:7.20.4; sn:hk.Search.layer</t>
+  </si>
+  <si>
+    <t>11:25:26|| view.SR1.Promotion| CityID:0;PromotionID:13%2C13%2C13%2C13%2C13%2C13%2C13%2C13%2C13%2C12%2C13%2C13%2C13%2C13%2C13%2C13;;Lang:zh_TW;Ver:7.20.4; sn:hk.LMS2.35336.tab.-990.1</t>
   </si>
   <si>
     <t>11:26:28|| or.search.adv| CityID:0;geo:22.2915762%2C114.2081518;LndID:35336;Page:1;sr:lmsSr1;Lang:zh_TW;Ver:7.20.4; sn:hk.AdvSearch</t>
   </si>
   <si>
-    <t>11:25:26|| view.SR1.Promotion| CityID:0;PromotionID:13%2C13%2C13%2C13%2C13%2C13%2C13%2C13%2C13%2C12%2C13%2C13%2C13%2C13%2C13%2C13;;Lang:zh_TW;Ver:7.20.4; sn:hk.LMS2.35336.tab.-990.1</t>
-  </si>
-  <si>
-    <t>11:25:26|| or.search.layer.search| CityID:0;geo:22.2915762%2C114.2081518;LndID:35336;Page:1;sr:lmsSr1;Lang:zh_TW;Ver:7.20.4; sn:hk.Search.layer</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Theme Listing</t>
-  </si>
-  <si>
-    <t>Brand Page</t>
-  </si>
-  <si>
-    <t>APP</t>
-  </si>
-  <si>
-    <t>view.SR1.Promotion</t>
-  </si>
-  <si>
-    <t>CityID:0;PromotionId:13,13,13,13,13,13,13,13,13,13,13,13,13,13,13;Sn:https://www.openrice.com/zh/hongkong/restaurants/type/%E5%B0%91%E9%B9%BD%E5%B0%91%E7%B3%96%E9%A3%9F%E5%BA%97?sortBy=ORScoreDesc</t>
-  </si>
-  <si>
-    <t>CityID:0;PromotionId:13,13,13,13,13,13,13,13,13,13,13,13,13,13,13;Sn:https://www.openrice.com/zh/hongkong/l-%E5%B0%91%E9%B9%BD%E5%B0%91%E7%B3%96%E9%A3%9F%E5%BA%97-l35336?sortBy=ORScoreDesc</t>
-  </si>
-  <si>
-    <t>CityID:0;PromotionId:13,13,13,13,13,13,13,13,13,13,13,13,13,13,13;Sn:https://www.openrice.com/zh/hongkong/l-%E5%B0%91%E9%B9%BD%E5%B0%91%E7%B3%96%E9%A3%9F%E5%BA%97-l35336</t>
-  </si>
-  <si>
-    <t>web</t>
-  </si>
-  <si>
-    <t>3. Daily Theme Listing Impressions (adv search)</t>
-  </si>
-  <si>
-    <t>2. Daily Brand Page (LMS) Pageview/ Impressions</t>
+    <t>11:26:28|| view.SR1.Promotion| CityID:0;PromotionID:13%2C13%2C13%2C13%2C13%2C13%2C13%2C13%2C13%2C12%2C13%2C13%2C13%2C13%2C13%2C13;;Lang:zh_TW;Ver:7.20.4; sn:hk.LMS2.35336.tab.-990.1</t>
   </si>
 </sst>
 </file>
@@ -234,9 +234,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -246,9 +243,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -281,7 +279,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE02D53A-CF6B-45CA-A7E1-C7F605E8F568}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -303,78 +301,13 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="Rectangle 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2615B815-D743-404E-BD89-664966F1D949}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2581275" y="2314575"/>
-          <a:ext cx="695325" cy="790575"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="57150" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:srgbClr val="00B0F0"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:round/>
-          <a:headEnd type="none" w="med" len="med"/>
-          <a:tailEnd type="none" w="med" len="med"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="accent2"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -388,7 +321,7 @@
         <xdr:cNvPr id="4" name="Picture 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D4BB82A-C4BE-4CE9-B828-4D18654AEA86}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -410,78 +343,13 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>590550</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="Rectangle 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C6E85AF-A1A6-4CDE-882F-452EF3F905EC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4533900" y="8505825"/>
-          <a:ext cx="933450" cy="361950"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="57150" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:srgbClr val="00B0F0"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:round/>
-          <a:headEnd type="none" w="med" len="med"/>
-          <a:tailEnd type="none" w="med" len="med"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="accent2"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -495,7 +363,7 @@
         <xdr:cNvPr id="6" name="Picture 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A0B9672-354D-4322-8DC1-1CF02A56B2E7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000006000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -517,6 +385,9 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -534,7 +405,7 @@
         <xdr:cNvPr id="7" name="Picture 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EAFEEAD5-C53B-414D-AB41-2BE75353D282}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000007000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -556,78 +427,13 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>523875</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>542925</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="Rectangle 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{84D54966-7A7A-4238-B8B4-DC5C9EACF3CB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2962275" y="13030200"/>
-          <a:ext cx="628650" cy="381000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="57150" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:srgbClr val="00B0F0"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:round/>
-          <a:headEnd type="none" w="med" len="med"/>
-          <a:tailEnd type="none" w="med" len="med"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="accent2"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -641,7 +447,7 @@
         <xdr:cNvPr id="9" name="Picture 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B05D29BA-7AA3-439A-B50A-8F501257501C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000009000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -650,13 +456,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -669,6 +469,9 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -686,7 +489,7 @@
         <xdr:cNvPr id="10" name="Picture 9">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{789C4471-EB49-4CA1-836C-15452BC4483E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000A000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -695,13 +498,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -714,146 +511,13 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>102</xdr:row>
-      <xdr:rowOff>19049</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
-      <xdr:row>106</xdr:row>
-      <xdr:rowOff>47624</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="Rectangle 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{48B58725-0A02-4EDB-8A1E-48842332D853}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="685800" y="19450049"/>
-          <a:ext cx="800100" cy="790575"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="57150" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:srgbClr val="00B0F0"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:round/>
-          <a:headEnd type="none" w="med" len="med"/>
-          <a:tailEnd type="none" w="med" len="med"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="accent2"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>130950</xdr:colOff>
-      <xdr:row>102</xdr:row>
-      <xdr:rowOff>35698</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>438149</xdr:colOff>
-      <xdr:row>104</xdr:row>
-      <xdr:rowOff>38099</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="Rectangle 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21987901-F75E-4BC0-B57F-750A581619F9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6226950" y="19466698"/>
-          <a:ext cx="916799" cy="383401"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="57150" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:srgbClr val="00B0F0"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:round/>
-          <a:headEnd type="none" w="med" len="med"/>
-          <a:tailEnd type="none" w="med" len="med"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="accent2"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1754,341 +1418,341 @@
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="7">
+      <c r="A38" s="15">
         <v>46235</v>
       </c>
       <c r="B38" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C38" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="7">
+      <c r="A39" s="15">
         <v>46236</v>
       </c>
       <c r="B39" s="5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C39" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="7">
+      <c r="A40" s="15">
         <v>46237</v>
       </c>
       <c r="B40" s="5">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="C40" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="7">
+      <c r="A41" s="15">
         <v>46238</v>
       </c>
       <c r="B41" s="5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C41" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="7">
+      <c r="A42" s="15">
         <v>46239</v>
       </c>
       <c r="B42" s="5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C42" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="7">
+      <c r="A43" s="15">
         <v>46240</v>
       </c>
       <c r="B43" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C43" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="7">
+      <c r="A44" s="15">
         <v>46241</v>
       </c>
       <c r="B44" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C44" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="7">
+      <c r="A45" s="15">
         <v>46242</v>
       </c>
       <c r="B45" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C45" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="7">
+      <c r="A46" s="15">
         <v>46243</v>
       </c>
       <c r="B46" s="5">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C46" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="7">
+      <c r="A47" s="15">
         <v>46244</v>
       </c>
       <c r="B47" s="5">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="C47" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="7">
+      <c r="A48" s="15">
         <v>46245</v>
       </c>
       <c r="B48" s="5">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C48" s="5">
         <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="7">
+      <c r="A49" s="15">
         <v>46246</v>
       </c>
       <c r="B49" s="5">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C49" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="7">
+      <c r="A50" s="15">
         <v>46247</v>
       </c>
       <c r="B50" s="5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C50" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="7">
+      <c r="A51" s="15">
         <v>46248</v>
       </c>
       <c r="B51" s="5">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="C51" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="7">
+      <c r="A52" s="15">
         <v>46249</v>
       </c>
       <c r="B52" s="5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C52" s="5">
         <v>11</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="7">
+      <c r="A53" s="15">
         <v>46250</v>
       </c>
       <c r="B53" s="5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C53" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="7">
+      <c r="A54" s="15">
         <v>46251</v>
       </c>
       <c r="B54" s="5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C54" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="7">
+      <c r="A55" s="15">
         <v>46252</v>
       </c>
       <c r="B55" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C55" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="7">
+      <c r="A56" s="15">
         <v>46253</v>
       </c>
       <c r="B56" s="5">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C56" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="7">
+      <c r="A57" s="15">
         <v>46254</v>
       </c>
       <c r="B57" s="5">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="C57" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="7">
+      <c r="A58" s="15">
         <v>46255</v>
       </c>
       <c r="B58" s="5">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C58" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="7">
+      <c r="A59" s="15">
         <v>46256</v>
       </c>
       <c r="B59" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C59" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="7">
+      <c r="A60" s="15">
         <v>46257</v>
       </c>
       <c r="B60" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C60" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="7">
+      <c r="A61" s="15">
         <v>46258</v>
       </c>
       <c r="B61" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C61" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="7">
+      <c r="A62" s="15">
         <v>46259</v>
       </c>
       <c r="B62" s="5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C62" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="7">
+      <c r="A63" s="15">
         <v>46260</v>
       </c>
       <c r="B63" s="5">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C63" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="7">
+      <c r="A64" s="15">
         <v>46261</v>
       </c>
       <c r="B64" s="5">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="C64" s="5">
         <v>17</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="7">
+      <c r="A65" s="15">
         <v>46262</v>
       </c>
       <c r="B65" s="5">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="C65" s="5">
         <v>68</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="7">
+      <c r="A66" s="15">
         <v>46263</v>
       </c>
       <c r="B66" s="5">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="C66" s="5">
         <v>61</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="7">
+      <c r="A67" s="15">
         <v>46264</v>
       </c>
       <c r="B67" s="5">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="C67" s="5">
         <v>52</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="7">
+      <c r="A68" s="15">
         <v>46265</v>
       </c>
       <c r="B68" s="5">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="C68" s="5">
         <v>31</v>
@@ -2111,7 +1775,7 @@
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="7">
+      <c r="A73" s="15">
         <v>46235</v>
       </c>
       <c r="B73" s="5">
@@ -2122,7 +1786,7 @@
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="7">
+      <c r="A74" s="15">
         <v>46236</v>
       </c>
       <c r="B74" s="5">
@@ -2133,7 +1797,7 @@
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="7">
+      <c r="A75" s="15">
         <v>46237</v>
       </c>
       <c r="B75" s="5">
@@ -2144,7 +1808,7 @@
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="7">
+      <c r="A76" s="15">
         <v>46238</v>
       </c>
       <c r="B76" s="5">
@@ -2155,7 +1819,7 @@
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="7">
+      <c r="A77" s="15">
         <v>46239</v>
       </c>
       <c r="B77" s="5">
@@ -2166,7 +1830,7 @@
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="7">
+      <c r="A78" s="15">
         <v>46240</v>
       </c>
       <c r="B78" s="5">
@@ -2177,7 +1841,7 @@
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="7">
+      <c r="A79" s="15">
         <v>46241</v>
       </c>
       <c r="B79" s="5">
@@ -2188,7 +1852,7 @@
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="7">
+      <c r="A80" s="15">
         <v>46242</v>
       </c>
       <c r="B80" s="5">
@@ -2199,7 +1863,7 @@
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="7">
+      <c r="A81" s="15">
         <v>46243</v>
       </c>
       <c r="B81" s="5">
@@ -2210,7 +1874,7 @@
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="7">
+      <c r="A82" s="15">
         <v>46244</v>
       </c>
       <c r="B82" s="5">
@@ -2221,7 +1885,7 @@
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="7">
+      <c r="A83" s="15">
         <v>46245</v>
       </c>
       <c r="B83" s="5">
@@ -2232,7 +1896,7 @@
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="7">
+      <c r="A84" s="15">
         <v>46246</v>
       </c>
       <c r="B84" s="5">
@@ -2243,7 +1907,7 @@
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="7">
+      <c r="A85" s="15">
         <v>46247</v>
       </c>
       <c r="B85" s="5">
@@ -2254,7 +1918,7 @@
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="7">
+      <c r="A86" s="15">
         <v>46248</v>
       </c>
       <c r="B86" s="5">
@@ -2265,7 +1929,7 @@
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="7">
+      <c r="A87" s="15">
         <v>46249</v>
       </c>
       <c r="B87" s="5">
@@ -2276,7 +1940,7 @@
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="7">
+      <c r="A88" s="15">
         <v>46250</v>
       </c>
       <c r="B88" s="5">
@@ -2287,7 +1951,7 @@
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="7">
+      <c r="A89" s="15">
         <v>46251</v>
       </c>
       <c r="B89" s="5">
@@ -2298,7 +1962,7 @@
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="7">
+      <c r="A90" s="15">
         <v>46252</v>
       </c>
       <c r="B90" s="5">
@@ -2309,7 +1973,7 @@
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="7">
+      <c r="A91" s="15">
         <v>46253</v>
       </c>
       <c r="B91" s="5">
@@ -2320,7 +1984,7 @@
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="7">
+      <c r="A92" s="15">
         <v>46254</v>
       </c>
       <c r="B92" s="5">
@@ -2331,7 +1995,7 @@
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="7">
+      <c r="A93" s="15">
         <v>46255</v>
       </c>
       <c r="B93" s="5">
@@ -2342,7 +2006,7 @@
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="7">
+      <c r="A94" s="15">
         <v>46256</v>
       </c>
       <c r="B94" s="5">
@@ -2353,7 +2017,7 @@
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" s="7">
+      <c r="A95" s="15">
         <v>46257</v>
       </c>
       <c r="B95" s="5">
@@ -2364,7 +2028,7 @@
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" s="7">
+      <c r="A96" s="15">
         <v>46258</v>
       </c>
       <c r="B96" s="5">
@@ -2375,7 +2039,7 @@
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" s="7">
+      <c r="A97" s="15">
         <v>46259</v>
       </c>
       <c r="B97" s="5">
@@ -2386,7 +2050,7 @@
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" s="7">
+      <c r="A98" s="15">
         <v>46260</v>
       </c>
       <c r="B98" s="5">
@@ -2397,7 +2061,7 @@
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" s="7">
+      <c r="A99" s="15">
         <v>46261</v>
       </c>
       <c r="B99" s="5">
@@ -2408,7 +2072,7 @@
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" s="7">
+      <c r="A100" s="15">
         <v>46262</v>
       </c>
       <c r="B100" s="5">
@@ -2419,7 +2083,7 @@
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" s="7">
+      <c r="A101" s="15">
         <v>46263</v>
       </c>
       <c r="B101" s="5">
@@ -2430,7 +2094,7 @@
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" s="7">
+      <c r="A102" s="15">
         <v>46264</v>
       </c>
       <c r="B102" s="5">
@@ -2441,7 +2105,7 @@
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" s="7">
+      <c r="A103" s="15">
         <v>46265</v>
       </c>
       <c r="B103" s="5">
@@ -2458,20 +2122,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6481AA32-E548-4638-869F-90616D0BABAA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:X119"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
       <c r="E1" s="10"/>
       <c r="G1" s="9" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="H1" s="9"/>
       <c r="I1" s="9"/>
@@ -2480,7 +2144,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -2493,7 +2157,7 @@
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.25">
       <c r="K17" s="10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L17" s="10"/>
     </row>
@@ -2506,20 +2170,20 @@
       <c r="L19" s="10"/>
     </row>
     <row r="29" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B29" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="T29" s="12"/>
-    </row>
-    <row r="30" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="T30" s="11"/>
-    </row>
-    <row r="31" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="13"/>
-      <c r="T31" s="15"/>
+      <c r="B29" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="T29" s="11"/>
+    </row>
+    <row r="30" spans="2:20" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T30" s="14"/>
+    </row>
+    <row r="31" spans="2:20" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="12"/>
+      <c r="T31" s="14"/>
     </row>
     <row r="40" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M40" s="10"/>
@@ -2531,7 +2195,7 @@
     </row>
     <row r="42" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M42" s="10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N42" s="10"/>
     </row>
@@ -2544,23 +2208,23 @@
       <c r="N44" s="10"/>
     </row>
     <row r="55" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B55" s="12" t="s">
-        <v>18</v>
+      <c r="B55" s="11" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="56" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B56" s="11" t="s">
-        <v>16</v>
+      <c r="B56" s="14" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="57" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B57" s="11"/>
+      <c r="B57" s="14"/>
     </row>
     <row r="58" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B58" s="14"/>
-    </row>
-    <row r="59" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="13"/>
+      <c r="B58" s="13"/>
+    </row>
+    <row r="59" spans="2:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B59" s="12"/>
     </row>
     <row r="64" spans="2:24" x14ac:dyDescent="0.25">
       <c r="W64" s="9"/>
@@ -2572,7 +2236,7 @@
     </row>
     <row r="66" spans="23:24" x14ac:dyDescent="0.25">
       <c r="W66" s="9" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="X66" s="9"/>
     </row>
@@ -2585,18 +2249,18 @@
       <c r="X68" s="9"/>
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B83" s="12" t="s">
+      <c r="B83" s="11" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B84" s="11" t="s">
-        <v>16</v>
+      <c r="B84" s="14" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A88" s="10" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.25">
@@ -2613,11 +2277,11 @@
     </row>
     <row r="98" spans="6:16" x14ac:dyDescent="0.25">
       <c r="F98" s="10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G98" s="10"/>
       <c r="O98" s="9" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P98" s="9"/>
     </row>
@@ -2635,27 +2299,27 @@
     </row>
     <row r="115" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="116" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B116" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="118" spans="2:12" x14ac:dyDescent="0.25">
       <c r="L118" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="119" spans="2:12" x14ac:dyDescent="0.25">
       <c r="L119" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup orientation="portrait"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>